--- a/base_execucao/mudancas_empenhos.xlsx
+++ b/base_execucao/mudancas_empenhos.xlsx
@@ -413,70 +413,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>tipo_mudanca</t>
+          <t>Sigla Órgão</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dotacao</t>
+          <t>Processo SEI</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>codEmpenho</t>
+          <t>Tipo de Mudança</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>numProcesso</t>
+          <t>Dotação</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>numeroOriginalContrato</t>
+          <t>Código do Empenho</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>data_hora_extracao</t>
+          <t>Número do Contrato</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Data/Hora Extração</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6064.2022/0001391-7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>ADICIONADA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>49296</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>001/2022/SMDET</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6064.2022/0001391-7</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>001/2022/SMDET</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SMRI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6073.2025/0000600-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>73.10.07.212.4009.6695.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>36535</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>001/2025/SMRI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6076.2025/0000677-6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41271</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>025/2025-SMTUR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6064.2022/0001391-7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40911</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>001/2022/SMDET</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6064.2022/0001391-7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>49307</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6064.2022/0001391-7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>001/2022/SMDET</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>05/05/2026 16:33:58</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6076.2025/0000677-6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ADICIONADA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>74.10.23.695.4009.2640.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6157</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>025/2025-SMTUR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:06:07</t>
         </is>
       </c>
     </row>

--- a/base_execucao/mudancas_empenhos.xlsx
+++ b/base_execucao/mudancas_empenhos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,21 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Campo Alterado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Valor Anterior</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Valor Atualizado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Data/Hora Extração</t>
         </is>
       </c>
@@ -456,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SMDET - VAI TEC</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADICIONADA</t>
+          <t>MODIFICADA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,14 +501,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06/05/2026 15:06:07</t>
+          <t>valLiquidado</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>R$ 19.309.998,54</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMDET - VAI TEC</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,7 +533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADICIONADA</t>
+          <t>MODIFICADA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +543,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,192 +553,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/05/2026 15:06:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SMRI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6073.2025/0000600-1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ADICIONADA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>73.10.07.212.4009.6695.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>001/2025/SMRI</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>06/05/2026 15:06:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SMTUR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6076.2025/0000677-6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ADICIONADA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>41271</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>025/2025-SMTUR</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>06/05/2026 15:06:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6064.2022/0001391-7</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ADICIONADA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>40911</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>001/2022/SMDET</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>06/05/2026 15:06:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6064.2022/0001391-7</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ADICIONADA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>49307</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>001/2022/SMDET</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>06/05/2026 15:06:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SMTUR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6076.2025/0000677-6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ADICIONADA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>74.10.23.695.4009.2640.33903900.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>6157</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>025/2025-SMTUR</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>06/05/2026 15:06:07</t>
+          <t>valLiquidado</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>R$ 2.500.000,00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>

--- a/base_execucao/mudancas_empenhos.xlsx
+++ b/base_execucao/mudancas_empenhos.xlsx
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SMDET - ADE SAMPA</t>
+          <t>SMTUR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6064.2022/0001391-7</t>
+          <t>6076.2025/0000677-6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,44 +486,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>001/2022/SMDET</t>
+          <t>025/2025-SMTUR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>valLiquidado</t>
+          <t>valPagoExercicio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.000.000,00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R$ 19.309.998,54</t>
+          <t>R$ 8.000.000,00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMDET - ADE SAMPA</t>
+          <t>SMDET - VAI TEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>valLiquidado</t>
+          <t>valPagoExercicio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R$ 2.500.000,00</t>
+          <t>R$ 2.247.234,98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>

--- a/base_execucao/mudancas_empenhos.xlsx
+++ b/base_execucao/mudancas_empenhos.xlsx
@@ -1,34 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan Faita\Documents\GitHub\sof_adesampa\base_execucao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA843A27-6738-4342-A442-3ACE59FA7D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+  <si>
+    <t>Sigla Órgão</t>
+  </si>
+  <si>
+    <t>Processo SEI</t>
+  </si>
+  <si>
+    <t>Dotação</t>
+  </si>
+  <si>
+    <t>Código do Empenho</t>
+  </si>
+  <si>
+    <t>Número do Contrato</t>
+  </si>
+  <si>
+    <t>Campo Alterado</t>
+  </si>
+  <si>
+    <t>Valor Anterior</t>
+  </si>
+  <si>
+    <t>Valor Atualizado</t>
+  </si>
+  <si>
+    <t>Data/Hora Extração</t>
+  </si>
+  <si>
+    <t>SMDET - ADE SAMPA</t>
+  </si>
+  <si>
+    <t>6064.2022/0001391-7</t>
+  </si>
+  <si>
+    <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+  </si>
+  <si>
+    <t>51281</t>
+  </si>
+  <si>
+    <t>001/2022/SMDET</t>
+  </si>
+  <si>
+    <t>valEmpenhadoLiquido</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>R$ 2.500.000,00</t>
+  </si>
+  <si>
+    <t>2039</t>
+  </si>
+  <si>
+    <t>valLiquidado</t>
+  </si>
+  <si>
+    <t>R$ 24.103.582,69</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +115,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,168 +419,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sigla Órgão</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Processo SEI</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tipo de Mudança</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Dotação</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Código do Empenho</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Número do Contrato</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Campo Alterado</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Valor Anterior</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Valor Atualizado</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Data/Hora Extração</t>
-        </is>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SMTUR</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>6076.2025/0000677-6</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MODIFICADA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>41271</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>025/2025-SMTUR</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>valPagoExercicio</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>R$ 4.000.000,00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>R$ 8.000.000,00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>14/05/2026 11:36:24</t>
-        </is>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46163.678263888891</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6064.2022/0001391-7</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MODIFICADA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>49307</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>001/2022/SMDET</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>valPagoExercicio</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>R$ 2.247.234,98</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14/05/2026 11:36:24</t>
-        </is>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1">
+        <v>46163.678263888891</v>
       </c>
     </row>
   </sheetData>

--- a/base_execucao/mudancas_empenhos.xlsx
+++ b/base_execucao/mudancas_empenhos.xlsx
@@ -1,103 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan Faita\Documents\GitHub\sof_adesampa\base_execucao\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA843A27-6738-4342-A442-3ACE59FA7D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
-  <si>
-    <t>Sigla Órgão</t>
-  </si>
-  <si>
-    <t>Processo SEI</t>
-  </si>
-  <si>
-    <t>Dotação</t>
-  </si>
-  <si>
-    <t>Código do Empenho</t>
-  </si>
-  <si>
-    <t>Número do Contrato</t>
-  </si>
-  <si>
-    <t>Campo Alterado</t>
-  </si>
-  <si>
-    <t>Valor Anterior</t>
-  </si>
-  <si>
-    <t>Valor Atualizado</t>
-  </si>
-  <si>
-    <t>Data/Hora Extração</t>
-  </si>
-  <si>
-    <t>SMDET - ADE SAMPA</t>
-  </si>
-  <si>
-    <t>6064.2022/0001391-7</t>
-  </si>
-  <si>
-    <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
-  </si>
-  <si>
-    <t>51281</t>
-  </si>
-  <si>
-    <t>001/2022/SMDET</t>
-  </si>
-  <si>
-    <t>valEmpenhadoLiquido</t>
-  </si>
-  <si>
-    <t>R$ 0,00</t>
-  </si>
-  <si>
-    <t>R$ 2.500.000,00</t>
-  </si>
-  <si>
-    <t>2039</t>
-  </si>
-  <si>
-    <t>valLiquidado</t>
-  </si>
-  <si>
-    <t>R$ 24.103.582,69</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -115,23 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,98 +408,153 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sigla Órgão</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Processo SEI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Dotação</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Código do Empenho</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Número do Contrato</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Campo Alterado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Valor Anterior</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Valor Atualizado</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Data/Hora Extração</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46163.678263888891</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6076.2025/0000677-6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>41271</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>025/2025-SMTUR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>valPagoExercicio</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>R$ 8.000.000,00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>R$ 12.000.000,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10/06/2026 10:56:02</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1">
-        <v>46163.678263888891</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6076.2025/0000677-6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>41271</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>025/2025-SMTUR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>valLiquidado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R$ 8.000.000,00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R$ 12.000.000,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10/06/2026 10:56:02</t>
+        </is>
       </c>
     </row>
   </sheetData>
